--- a/output/Tables/2019/soc_1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/soc_1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>262.3275912296903</v>
+        <v>261.7983314755504</v>
       </c>
       <c r="B2">
-        <v>270.8291604878166</v>
+        <v>270.2538256737237</v>
       </c>
       <c r="C2">
-        <v>280.75625694296</v>
+        <v>280.1252195222892</v>
       </c>
       <c r="D2">
-        <v>0.1875642277292291</v>
+        <v>0.1871858070050191</v>
       </c>
       <c r="E2">
-        <v>0.1936428497487894</v>
+        <v>0.1932314853567131</v>
       </c>
       <c r="F2">
-        <v>0.2007407237142169</v>
+        <v>0.2002895319584373</v>
       </c>
       <c r="G2">
-        <v>2.344552846615364</v>
+        <v>2.339822587562739</v>
       </c>
       <c r="H2">
-        <v>2.420535621859867</v>
+        <v>2.415393566958913</v>
       </c>
       <c r="I2">
-        <v>2.509259046427712</v>
+        <v>2.503619149480467</v>
       </c>
       <c r="J2">
         <v>1</v>

--- a/output/Tables/2019/soc_1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/soc_1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>261.7983314755504</v>
+        <v>298.2770210401644</v>
       </c>
       <c r="B2">
-        <v>270.2538256737237</v>
+        <v>308.1781013522989</v>
       </c>
       <c r="C2">
-        <v>280.1252195222892</v>
+        <v>319.7540351759549</v>
       </c>
       <c r="D2">
-        <v>0.1871858070050191</v>
+        <v>0.2131811459993281</v>
       </c>
       <c r="E2">
-        <v>0.1932314853567131</v>
+        <v>0.2205777461397409</v>
       </c>
       <c r="F2">
-        <v>0.2002895319584373</v>
+        <v>0.2285234790435532</v>
       </c>
       <c r="G2">
-        <v>2.339822587562739</v>
+        <v>2.664764324991602</v>
       </c>
       <c r="H2">
-        <v>2.415393566958913</v>
+        <v>2.757221826746762</v>
       </c>
       <c r="I2">
-        <v>2.503619149480467</v>
+        <v>2.856543488044415</v>
       </c>
       <c r="J2">
         <v>1</v>
